--- a/LabGrymace/calibration/figure4bd_data.xlsx
+++ b/LabGrymace/calibration/figure4bd_data.xlsx
@@ -1,89 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/新加卷/Figure 4/Figure4B-D/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EFAF1A-04AC-B145-A195-F4E5BCD40212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Points" sheetId="1" r:id="rId1"/>
-    <sheet name="Fit" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fit" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="12">
-  <si>
-    <t>Behavior</t>
-  </si>
-  <si>
-    <t>Dose_mgkg</t>
-  </si>
-  <si>
-    <t>log10_dose</t>
-  </si>
-  <si>
-    <t>Intensity_Area</t>
-  </si>
-  <si>
-    <t>Ear Resting State</t>
-  </si>
-  <si>
-    <t>Orbital Tightening</t>
-  </si>
-  <si>
-    <t>Nose Bulging</t>
-  </si>
-  <si>
-    <t>n_points</t>
-  </si>
-  <si>
-    <t>Pearson_r</t>
-  </si>
-  <si>
-    <t>p_value</t>
-  </si>
-  <si>
-    <t>slope</t>
-  </si>
-  <si>
-    <t>intercept</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -117,25 +69,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -423,293 +434,117 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Behavior</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>n_points</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_r</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slope</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ear Resting State</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="C2" s="2">
-        <v>-2</v>
-      </c>
-      <c r="D2" s="2">
-        <v>8.9220000000000006</v>
+      <c r="C2" s="2" t="n">
+        <v>-0.993</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>-3.574</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2.03</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Orbital Tightening</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-1</v>
-      </c>
-      <c r="D3" s="2">
-        <v>6.0640000000000001</v>
+      <c r="C3" s="2" t="n">
+        <v>-0.987</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>-3.158</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>6.326</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nose Bulging</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>4</v>
       </c>
-      <c r="B4" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="C4" s="2">
-        <v>-0.30102999566398098</v>
-      </c>
-      <c r="D4" s="2">
-        <v>3.2730000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1.657</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="C6" s="2">
-        <v>-2</v>
-      </c>
-      <c r="D6" s="2">
-        <v>12.361000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="C7" s="2">
-        <v>-1</v>
-      </c>
-      <c r="D7" s="2">
-        <v>10.141999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-0.3010299956639812</v>
-      </c>
-      <c r="D8" s="2">
-        <v>6.9550000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2">
-        <v>6.2709999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2">
-        <v>0.01</v>
-      </c>
-      <c r="C10" s="2">
-        <v>-2</v>
-      </c>
-      <c r="D10" s="2">
-        <v>6.1440000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="C11" s="2">
-        <v>-1</v>
-      </c>
-      <c r="D11" s="2">
-        <v>3.1880000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="C12" s="2">
-        <v>-0.3010299956639812</v>
-      </c>
-      <c r="D12" s="2">
-        <v>3.109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>2.6040000000000001</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2">
-        <v>-0.99299999999999999</v>
-      </c>
-      <c r="D2" s="2">
-        <v>7.3000000000000001E-3</v>
-      </c>
-      <c r="E2" s="2">
-        <v>-3.5739999999999998</v>
-      </c>
-      <c r="F2" s="2">
-        <v>2.0299999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2">
-        <v>-0.98699999999999999</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1.29E-2</v>
-      </c>
-      <c r="E3" s="2">
-        <v>-3.1579999999999999</v>
-      </c>
-      <c r="F3" s="2">
-        <v>6.3259999999999996</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2">
-        <v>-0.93200000000000005</v>
-      </c>
-      <c r="D4" s="2">
-        <v>6.8199999999999997E-2</v>
-      </c>
-      <c r="E4" s="2">
-        <v>-1.6890000000000001</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2.3679999999999999</v>
+      <c r="C4" s="2" t="n">
+        <v>-0.9320000000000001</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>-1.689</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2.368</v>
       </c>
     </row>
   </sheetData>
